--- a/excel-files/PASIG/SAN LORENZO RUIZ ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/PASIG/SAN LORENZO RUIZ ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\WEB\LR\excel-files\PASIG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BB8489-BF0E-4535-B4DC-EBE3F98F70E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="441" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE481C61-1418-4BDE-A3B8-980D12B02B0B}"/>
   <bookViews>
-    <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="8880" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -1881,6 +1881,13 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1904,13 +1911,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -2989,6 +2989,13 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3025,13 +3032,6 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3074,7 +3074,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3091,7 +3091,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
@@ -3147,7 +3147,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
@@ -3520,22 +3520,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AQ123"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.88671875" customWidth="1"/>
-    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.109375" customWidth="1"/>
-    <col min="11" max="11" width="17.6640625" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
-    <col min="13" max="14" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="13" max="14" width="15.85546875" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="14" customFormat="1" ht="64.95" customHeight="1">
+    <row r="1" spans="1:43" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3844,7 +3844,7 @@
       <c r="AP5" s="42"/>
       <c r="AQ5" s="42"/>
     </row>
-    <row r="6" spans="1:43" ht="19.2">
+    <row r="6" spans="1:43" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3900,7 +3900,7 @@
       <c r="AP6" s="42"/>
       <c r="AQ6" s="42"/>
     </row>
-    <row r="7" spans="1:43">
+    <row r="7" spans="1:43" ht="15">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -4171,7 +4171,7 @@
       <c r="AP11" s="42"/>
       <c r="AQ11" s="42"/>
     </row>
-    <row r="12" spans="1:43" ht="19.2">
+    <row r="12" spans="1:43" ht="19.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -4227,7 +4227,7 @@
       <c r="AP12" s="42"/>
       <c r="AQ12" s="42"/>
     </row>
-    <row r="13" spans="1:43">
+    <row r="13" spans="1:43" ht="15">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -4550,7 +4550,7 @@
       <c r="AP18" s="42"/>
       <c r="AQ18" s="42"/>
     </row>
-    <row r="19" spans="1:43" ht="19.2">
+    <row r="19" spans="1:43" ht="19.5">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -4606,7 +4606,7 @@
       <c r="AP19" s="42"/>
       <c r="AQ19" s="42"/>
     </row>
-    <row r="20" spans="1:43" ht="13.95" customHeight="1">
+    <row r="20" spans="1:43" ht="13.9" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -4774,7 +4774,7 @@
       <c r="AP22" s="42"/>
       <c r="AQ22" s="42"/>
     </row>
-    <row r="23" spans="1:43" ht="19.2">
+    <row r="23" spans="1:43" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -8768,7 +8768,7 @@
       <c r="AP95" s="42"/>
       <c r="AQ95" s="42"/>
     </row>
-    <row r="96" spans="1:43" ht="38.4">
+    <row r="96" spans="1:43" ht="38.25">
       <c r="A96" s="1" t="s">
         <v>25</v>
       </c>
@@ -9839,8 +9839,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -9855,36 +9855,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:AA127"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" customWidth="1"/>
-    <col min="2" max="2" width="27.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" customWidth="1"/>
-    <col min="4" max="4" width="26.109375" customWidth="1"/>
-    <col min="5" max="5" width="23.109375" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5546875" customWidth="1"/>
-    <col min="8" max="9" width="20.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="35.5546875" customWidth="1"/>
-    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.5546875" customWidth="1"/>
-    <col min="14" max="15" width="20.88671875" customWidth="1"/>
-    <col min="16" max="16" width="21.5546875" customWidth="1"/>
-    <col min="17" max="17" width="33.44140625" customWidth="1"/>
-    <col min="18" max="18" width="25.88671875" customWidth="1"/>
-    <col min="19" max="19" width="32.88671875" customWidth="1"/>
-    <col min="20" max="21" width="20.88671875" customWidth="1"/>
-    <col min="22" max="22" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="35.5703125" customWidth="1"/>
+    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.5703125" customWidth="1"/>
+    <col min="14" max="15" width="20.85546875" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" customWidth="1"/>
+    <col min="17" max="17" width="33.42578125" customWidth="1"/>
+    <col min="18" max="18" width="25.85546875" customWidth="1"/>
+    <col min="19" max="19" width="32.85546875" customWidth="1"/>
+    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" customWidth="1"/>
     <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.33203125" customWidth="1"/>
-    <col min="25" max="25" width="20.88671875" customWidth="1"/>
-    <col min="26" max="26" width="14.88671875" customWidth="1"/>
-    <col min="27" max="27" width="15.109375" customWidth="1"/>
+    <col min="24" max="24" width="15.28515625" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.200000000000003" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="D1" s="50" t="s">
         <v>34</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -10151,7 +10151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.2">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -10222,7 +10222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.2">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -10293,7 +10293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.2">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -10364,7 +10364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.2">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -10435,7 +10435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.2">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.2">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -10577,7 +10577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.2">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -10661,7 +10661,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="38.4">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -10732,7 +10732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.2">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.2">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.2">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -10957,7 +10957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.2">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -11028,7 +11028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.2">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -11117,7 +11117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.2">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -11188,7 +11188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.2">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -11259,7 +11259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -11273,7 +11273,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="38.4">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.2">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.2">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -11486,7 +11486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.2">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -11563,7 +11563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.2">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -11640,7 +11640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.2">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -11717,7 +11717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.2">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -11794,7 +11794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.2">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -11865,7 +11865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.2">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -11950,7 +11950,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.2">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -12021,7 +12021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.2">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -12092,7 +12092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.2">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -12163,7 +12163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.2">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -12234,7 +12234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="38.4">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -12305,7 +12305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.2">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.2">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -12447,7 +12447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.2">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -12518,7 +12518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.2">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -12589,7 +12589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -12603,7 +12603,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.2">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -12680,7 +12680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.2">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -12751,7 +12751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.2">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -12765,12 +12765,14 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3168</v>
       </c>
-      <c r="E45" s="5"/>
+      <c r="E45" s="5">
+        <v>154</v>
+      </c>
       <c r="F45" s="1"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
         <f t="shared" si="2"/>
-        <v>3168</v>
+        <v>3014</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="3"/>
@@ -12828,7 +12830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.2">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -12899,7 +12901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.4">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -12976,7 +12978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.2">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -13047,7 +13049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.2">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -13124,7 +13126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.2">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -13195,7 +13197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.2">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -13272,7 +13274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -13286,7 +13288,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.2">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -13357,7 +13359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.2">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -13428,7 +13430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.2">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -13499,7 +13501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.2">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -13570,7 +13572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="38.4">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -13641,7 +13643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.2">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -13712,7 +13714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.2">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -13783,7 +13785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.2">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -13854,7 +13856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.2">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -13925,7 +13927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -13939,7 +13941,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.2">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -14010,7 +14012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.2">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -14081,7 +14083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.2">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -14152,7 +14154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.2">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -14223,7 +14225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="38.4">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -14294,7 +14296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.2">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -14365,7 +14367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.2">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -14436,7 +14438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.2">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -14507,7 +14509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.2">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -14578,7 +14580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -14592,7 +14594,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.2">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -14663,7 +14665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.2">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -14734,7 +14736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.2">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -14805,7 +14807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.2">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -14876,7 +14878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.2">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -14947,7 +14949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.2">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -15018,7 +15020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.2">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -15089,7 +15091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.2">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -15160,7 +15162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.2">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -15231,7 +15233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -15245,7 +15247,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.2">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -15316,7 +15318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.2">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -15387,7 +15389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.2">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -15458,7 +15460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.2">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -15529,7 +15531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.2">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -15600,7 +15602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.2">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -15671,7 +15673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.2">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -15742,7 +15744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.2">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -15813,7 +15815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.2">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -15884,7 +15886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -15898,7 +15900,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.2">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -15916,11 +15918,11 @@
       <c r="F93" s="10"/>
       <c r="G93" s="12"/>
       <c r="H93" s="12">
-        <f t="shared" ref="H93:H101" si="24">IF((D93-E93)&lt;0,0,(D93-E93))</f>
+        <f>IF((D93-E93)&lt;0,0,(D93-E93))</f>
         <v>0</v>
       </c>
       <c r="I93" s="12">
-        <f t="shared" ref="I93:I101" si="25">IF((E93-D93)&lt;0,0,(E93-D93))</f>
+        <f>IF((E93-D93)&lt;0,0,(E93-D93))</f>
         <v>0</v>
       </c>
       <c r="J93" s="12">
@@ -15931,11 +15933,11 @@
       <c r="L93" s="10"/>
       <c r="M93" s="12"/>
       <c r="N93" s="12">
-        <f t="shared" ref="N93:N101" si="26">IF((J93-K93)&lt;0,0,(J93-K93))</f>
+        <f>IF((J93-K93)&lt;0,0,(J93-K93))</f>
         <v>0</v>
       </c>
       <c r="O93" s="12">
-        <f t="shared" ref="O93:O101" si="27">IF((K93-J93)&lt;0,0,(K93-J93))</f>
+        <f>IF((K93-J93)&lt;0,0,(K93-J93))</f>
         <v>0</v>
       </c>
       <c r="P93" s="12">
@@ -15946,11 +15948,11 @@
       <c r="R93" s="10"/>
       <c r="S93" s="12"/>
       <c r="T93" s="12">
-        <f t="shared" ref="T93:T101" si="28">IF((P93-Q93)&lt;0,0,(P93-Q93))</f>
+        <f>IF((P93-Q93)&lt;0,0,(P93-Q93))</f>
         <v>0</v>
       </c>
       <c r="U93" s="12">
-        <f t="shared" ref="U93:U101" si="29">IF((Q93-P93)&lt;0,0,(Q93-P93))</f>
+        <f>IF((Q93-P93)&lt;0,0,(Q93-P93))</f>
         <v>0</v>
       </c>
       <c r="V93" s="12">
@@ -15961,15 +15963,15 @@
       <c r="X93" s="10"/>
       <c r="Y93" s="12"/>
       <c r="Z93" s="12">
-        <f t="shared" ref="Z93:Z101" si="30">IF((V93-W93)&lt;0,0,(V93-W93))</f>
+        <f>IF((V93-W93)&lt;0,0,(V93-W93))</f>
         <v>0</v>
       </c>
       <c r="AA93" s="12">
-        <f t="shared" ref="AA93:AA101" si="31">IF((W93-V93)&lt;0,0,(W93-V93))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" ht="19.2">
+        <f>IF((W93-V93)&lt;0,0,(W93-V93))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -15987,11 +15989,11 @@
       <c r="F94" s="10"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12">
-        <f t="shared" si="24"/>
+        <f>IF((D94-E94)&lt;0,0,(D94-E94))</f>
         <v>0</v>
       </c>
       <c r="I94" s="12">
-        <f t="shared" si="25"/>
+        <f>IF((E94-D94)&lt;0,0,(E94-D94))</f>
         <v>0</v>
       </c>
       <c r="J94" s="12">
@@ -16002,11 +16004,11 @@
       <c r="L94" s="10"/>
       <c r="M94" s="12"/>
       <c r="N94" s="12">
-        <f t="shared" si="26"/>
+        <f>IF((J94-K94)&lt;0,0,(J94-K94))</f>
         <v>0</v>
       </c>
       <c r="O94" s="12">
-        <f t="shared" si="27"/>
+        <f>IF((K94-J94)&lt;0,0,(K94-J94))</f>
         <v>0</v>
       </c>
       <c r="P94" s="12">
@@ -16017,11 +16019,11 @@
       <c r="R94" s="10"/>
       <c r="S94" s="12"/>
       <c r="T94" s="12">
-        <f t="shared" si="28"/>
+        <f>IF((P94-Q94)&lt;0,0,(P94-Q94))</f>
         <v>0</v>
       </c>
       <c r="U94" s="12">
-        <f t="shared" si="29"/>
+        <f>IF((Q94-P94)&lt;0,0,(Q94-P94))</f>
         <v>0</v>
       </c>
       <c r="V94" s="12">
@@ -16032,15 +16034,15 @@
       <c r="X94" s="10"/>
       <c r="Y94" s="12"/>
       <c r="Z94" s="12">
-        <f t="shared" si="30"/>
+        <f>IF((V94-W94)&lt;0,0,(V94-W94))</f>
         <v>0</v>
       </c>
       <c r="AA94" s="12">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:27" ht="19.2">
+        <f>IF((W94-V94)&lt;0,0,(W94-V94))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -16058,11 +16060,11 @@
       <c r="F95" s="10"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12">
-        <f t="shared" si="24"/>
+        <f>IF((D95-E95)&lt;0,0,(D95-E95))</f>
         <v>0</v>
       </c>
       <c r="I95" s="12">
-        <f t="shared" si="25"/>
+        <f>IF((E95-D95)&lt;0,0,(E95-D95))</f>
         <v>0</v>
       </c>
       <c r="J95" s="12">
@@ -16073,11 +16075,11 @@
       <c r="L95" s="10"/>
       <c r="M95" s="12"/>
       <c r="N95" s="12">
-        <f t="shared" si="26"/>
+        <f>IF((J95-K95)&lt;0,0,(J95-K95))</f>
         <v>0</v>
       </c>
       <c r="O95" s="12">
-        <f t="shared" si="27"/>
+        <f>IF((K95-J95)&lt;0,0,(K95-J95))</f>
         <v>0</v>
       </c>
       <c r="P95" s="12">
@@ -16088,11 +16090,11 @@
       <c r="R95" s="10"/>
       <c r="S95" s="12"/>
       <c r="T95" s="12">
-        <f t="shared" si="28"/>
+        <f>IF((P95-Q95)&lt;0,0,(P95-Q95))</f>
         <v>0</v>
       </c>
       <c r="U95" s="12">
-        <f t="shared" si="29"/>
+        <f>IF((Q95-P95)&lt;0,0,(Q95-P95))</f>
         <v>0</v>
       </c>
       <c r="V95" s="12">
@@ -16103,15 +16105,15 @@
       <c r="X95" s="10"/>
       <c r="Y95" s="12"/>
       <c r="Z95" s="12">
-        <f t="shared" si="30"/>
+        <f>IF((V95-W95)&lt;0,0,(V95-W95))</f>
         <v>0</v>
       </c>
       <c r="AA95" s="12">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" ht="19.2">
+        <f>IF((W95-V95)&lt;0,0,(W95-V95))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -16129,11 +16131,11 @@
       <c r="F96" s="10"/>
       <c r="G96" s="12"/>
       <c r="H96" s="12">
-        <f t="shared" si="24"/>
+        <f>IF((D96-E96)&lt;0,0,(D96-E96))</f>
         <v>0</v>
       </c>
       <c r="I96" s="12">
-        <f t="shared" si="25"/>
+        <f>IF((E96-D96)&lt;0,0,(E96-D96))</f>
         <v>0</v>
       </c>
       <c r="J96" s="12">
@@ -16144,11 +16146,11 @@
       <c r="L96" s="10"/>
       <c r="M96" s="12"/>
       <c r="N96" s="12">
-        <f t="shared" si="26"/>
+        <f>IF((J96-K96)&lt;0,0,(J96-K96))</f>
         <v>0</v>
       </c>
       <c r="O96" s="12">
-        <f t="shared" si="27"/>
+        <f>IF((K96-J96)&lt;0,0,(K96-J96))</f>
         <v>0</v>
       </c>
       <c r="P96" s="12">
@@ -16159,11 +16161,11 @@
       <c r="R96" s="10"/>
       <c r="S96" s="12"/>
       <c r="T96" s="12">
-        <f t="shared" si="28"/>
+        <f>IF((P96-Q96)&lt;0,0,(P96-Q96))</f>
         <v>0</v>
       </c>
       <c r="U96" s="12">
-        <f t="shared" si="29"/>
+        <f>IF((Q96-P96)&lt;0,0,(Q96-P96))</f>
         <v>0</v>
       </c>
       <c r="V96" s="12">
@@ -16174,15 +16176,15 @@
       <c r="X96" s="10"/>
       <c r="Y96" s="12"/>
       <c r="Z96" s="12">
-        <f t="shared" si="30"/>
+        <f>IF((V96-W96)&lt;0,0,(V96-W96))</f>
         <v>0</v>
       </c>
       <c r="AA96" s="12">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" ht="19.2">
+        <f>IF((W96-V96)&lt;0,0,(W96-V96))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -16200,11 +16202,11 @@
       <c r="F97" s="10"/>
       <c r="G97" s="12"/>
       <c r="H97" s="12">
-        <f t="shared" si="24"/>
+        <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
         <v>0</v>
       </c>
       <c r="I97" s="12">
-        <f t="shared" si="25"/>
+        <f>IF((E97-D97)&lt;0,0,(E97-D97))</f>
         <v>0</v>
       </c>
       <c r="J97" s="12">
@@ -16215,11 +16217,11 @@
       <c r="L97" s="10"/>
       <c r="M97" s="12"/>
       <c r="N97" s="12">
-        <f t="shared" si="26"/>
+        <f>IF((J97-K97)&lt;0,0,(J97-K97))</f>
         <v>0</v>
       </c>
       <c r="O97" s="12">
-        <f t="shared" si="27"/>
+        <f>IF((K97-J97)&lt;0,0,(K97-J97))</f>
         <v>0</v>
       </c>
       <c r="P97" s="12">
@@ -16230,11 +16232,11 @@
       <c r="R97" s="10"/>
       <c r="S97" s="12"/>
       <c r="T97" s="12">
-        <f t="shared" si="28"/>
+        <f>IF((P97-Q97)&lt;0,0,(P97-Q97))</f>
         <v>0</v>
       </c>
       <c r="U97" s="12">
-        <f t="shared" si="29"/>
+        <f>IF((Q97-P97)&lt;0,0,(Q97-P97))</f>
         <v>0</v>
       </c>
       <c r="V97" s="12">
@@ -16245,15 +16247,15 @@
       <c r="X97" s="10"/>
       <c r="Y97" s="12"/>
       <c r="Z97" s="12">
-        <f t="shared" si="30"/>
+        <f>IF((V97-W97)&lt;0,0,(V97-W97))</f>
         <v>0</v>
       </c>
       <c r="AA97" s="12">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:27" ht="19.2">
+        <f>IF((W97-V97)&lt;0,0,(W97-V97))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -16271,11 +16273,11 @@
       <c r="F98" s="10"/>
       <c r="G98" s="12"/>
       <c r="H98" s="12">
-        <f t="shared" si="24"/>
+        <f>IF((D98-E98)&lt;0,0,(D98-E98))</f>
         <v>0</v>
       </c>
       <c r="I98" s="12">
-        <f t="shared" si="25"/>
+        <f>IF((E98-D98)&lt;0,0,(E98-D98))</f>
         <v>0</v>
       </c>
       <c r="J98" s="12">
@@ -16286,11 +16288,11 @@
       <c r="L98" s="10"/>
       <c r="M98" s="12"/>
       <c r="N98" s="12">
-        <f t="shared" si="26"/>
+        <f>IF((J98-K98)&lt;0,0,(J98-K98))</f>
         <v>0</v>
       </c>
       <c r="O98" s="12">
-        <f t="shared" si="27"/>
+        <f>IF((K98-J98)&lt;0,0,(K98-J98))</f>
         <v>0</v>
       </c>
       <c r="P98" s="12">
@@ -16301,11 +16303,11 @@
       <c r="R98" s="10"/>
       <c r="S98" s="12"/>
       <c r="T98" s="12">
-        <f t="shared" si="28"/>
+        <f>IF((P98-Q98)&lt;0,0,(P98-Q98))</f>
         <v>0</v>
       </c>
       <c r="U98" s="12">
-        <f t="shared" si="29"/>
+        <f>IF((Q98-P98)&lt;0,0,(Q98-P98))</f>
         <v>0</v>
       </c>
       <c r="V98" s="12">
@@ -16316,15 +16318,15 @@
       <c r="X98" s="10"/>
       <c r="Y98" s="12"/>
       <c r="Z98" s="12">
-        <f t="shared" si="30"/>
+        <f>IF((V98-W98)&lt;0,0,(V98-W98))</f>
         <v>0</v>
       </c>
       <c r="AA98" s="12">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:27" ht="19.2">
+        <f>IF((W98-V98)&lt;0,0,(W98-V98))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -16342,11 +16344,11 @@
       <c r="F99" s="10"/>
       <c r="G99" s="12"/>
       <c r="H99" s="12">
-        <f t="shared" si="24"/>
+        <f>IF((D99-E99)&lt;0,0,(D99-E99))</f>
         <v>0</v>
       </c>
       <c r="I99" s="12">
-        <f t="shared" si="25"/>
+        <f>IF((E99-D99)&lt;0,0,(E99-D99))</f>
         <v>0</v>
       </c>
       <c r="J99" s="12">
@@ -16357,11 +16359,11 @@
       <c r="L99" s="10"/>
       <c r="M99" s="12"/>
       <c r="N99" s="12">
-        <f t="shared" si="26"/>
+        <f>IF((J99-K99)&lt;0,0,(J99-K99))</f>
         <v>0</v>
       </c>
       <c r="O99" s="12">
-        <f t="shared" si="27"/>
+        <f>IF((K99-J99)&lt;0,0,(K99-J99))</f>
         <v>0</v>
       </c>
       <c r="P99" s="12">
@@ -16372,11 +16374,11 @@
       <c r="R99" s="10"/>
       <c r="S99" s="12"/>
       <c r="T99" s="12">
-        <f t="shared" si="28"/>
+        <f>IF((P99-Q99)&lt;0,0,(P99-Q99))</f>
         <v>0</v>
       </c>
       <c r="U99" s="12">
-        <f t="shared" si="29"/>
+        <f>IF((Q99-P99)&lt;0,0,(Q99-P99))</f>
         <v>0</v>
       </c>
       <c r="V99" s="12">
@@ -16387,15 +16389,15 @@
       <c r="X99" s="10"/>
       <c r="Y99" s="12"/>
       <c r="Z99" s="12">
-        <f t="shared" si="30"/>
+        <f>IF((V99-W99)&lt;0,0,(V99-W99))</f>
         <v>0</v>
       </c>
       <c r="AA99" s="12">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:27" ht="19.2">
+        <f>IF((W99-V99)&lt;0,0,(W99-V99))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -16413,11 +16415,11 @@
       <c r="F100" s="10"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12">
-        <f t="shared" si="24"/>
+        <f>IF((D100-E100)&lt;0,0,(D100-E100))</f>
         <v>0</v>
       </c>
       <c r="I100" s="12">
-        <f t="shared" si="25"/>
+        <f>IF((E100-D100)&lt;0,0,(E100-D100))</f>
         <v>0</v>
       </c>
       <c r="J100" s="12">
@@ -16428,11 +16430,11 @@
       <c r="L100" s="10"/>
       <c r="M100" s="12"/>
       <c r="N100" s="12">
-        <f t="shared" si="26"/>
+        <f>IF((J100-K100)&lt;0,0,(J100-K100))</f>
         <v>0</v>
       </c>
       <c r="O100" s="12">
-        <f t="shared" si="27"/>
+        <f>IF((K100-J100)&lt;0,0,(K100-J100))</f>
         <v>0</v>
       </c>
       <c r="P100" s="12">
@@ -16443,11 +16445,11 @@
       <c r="R100" s="10"/>
       <c r="S100" s="12"/>
       <c r="T100" s="12">
-        <f t="shared" si="28"/>
+        <f>IF((P100-Q100)&lt;0,0,(P100-Q100))</f>
         <v>0</v>
       </c>
       <c r="U100" s="12">
-        <f t="shared" si="29"/>
+        <f>IF((Q100-P100)&lt;0,0,(Q100-P100))</f>
         <v>0</v>
       </c>
       <c r="V100" s="12">
@@ -16458,15 +16460,15 @@
       <c r="X100" s="10"/>
       <c r="Y100" s="12"/>
       <c r="Z100" s="12">
-        <f t="shared" si="30"/>
+        <f>IF((V100-W100)&lt;0,0,(V100-W100))</f>
         <v>0</v>
       </c>
       <c r="AA100" s="12">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:27" ht="19.2">
+        <f>IF((W100-V100)&lt;0,0,(W100-V100))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -16484,11 +16486,11 @@
       <c r="F101" s="10"/>
       <c r="G101" s="12"/>
       <c r="H101" s="12">
-        <f t="shared" si="24"/>
+        <f>IF((D101-E101)&lt;0,0,(D101-E101))</f>
         <v>0</v>
       </c>
       <c r="I101" s="12">
-        <f t="shared" si="25"/>
+        <f>IF((E101-D101)&lt;0,0,(E101-D101))</f>
         <v>0</v>
       </c>
       <c r="J101" s="12">
@@ -16499,11 +16501,11 @@
       <c r="L101" s="10"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12">
-        <f t="shared" si="26"/>
+        <f>IF((J101-K101)&lt;0,0,(J101-K101))</f>
         <v>0</v>
       </c>
       <c r="O101" s="12">
-        <f t="shared" si="27"/>
+        <f>IF((K101-J101)&lt;0,0,(K101-J101))</f>
         <v>0</v>
       </c>
       <c r="P101" s="12">
@@ -16514,11 +16516,11 @@
       <c r="R101" s="10"/>
       <c r="S101" s="12"/>
       <c r="T101" s="12">
-        <f t="shared" si="28"/>
+        <f>IF((P101-Q101)&lt;0,0,(P101-Q101))</f>
         <v>0</v>
       </c>
       <c r="U101" s="12">
-        <f t="shared" si="29"/>
+        <f>IF((Q101-P101)&lt;0,0,(Q101-P101))</f>
         <v>0</v>
       </c>
       <c r="V101" s="12">
@@ -16529,15 +16531,15 @@
       <c r="X101" s="10"/>
       <c r="Y101" s="12"/>
       <c r="Z101" s="12">
-        <f t="shared" si="30"/>
+        <f>IF((V101-W101)&lt;0,0,(V101-W101))</f>
         <v>0</v>
       </c>
       <c r="AA101" s="12">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.2">
+        <f>IF((W101-V101)&lt;0,0,(W101-V101))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -16551,7 +16553,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.4">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>25</v>
       </c>
@@ -16622,7 +16624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.2">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>25</v>
       </c>
@@ -16693,7 +16695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.2">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>25</v>
       </c>
@@ -16764,7 +16766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.2">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>25</v>
       </c>
@@ -16835,7 +16837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.4">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>25</v>
       </c>
@@ -16906,7 +16908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="38.4">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>25</v>
       </c>
@@ -16977,7 +16979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="57.6">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>25</v>
       </c>
@@ -17048,7 +17050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.4">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>25</v>
       </c>
@@ -17119,7 +17121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -17130,7 +17132,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.2">
+    <row r="112" spans="1:27" ht="19.149999999999999">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -17192,7 +17194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.2">
+    <row r="113" spans="1:27" ht="19.149999999999999">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -17254,7 +17256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.2">
+    <row r="114" spans="1:27" ht="19.149999999999999">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -17316,7 +17318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.2">
+    <row r="115" spans="1:27" ht="19.149999999999999">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -17378,7 +17380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.2">
+    <row r="116" spans="1:27" ht="19.149999999999999">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -17440,7 +17442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.2">
+    <row r="117" spans="1:27" ht="19.149999999999999">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -17502,7 +17504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.2">
+    <row r="118" spans="1:27" ht="19.149999999999999">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -17564,7 +17566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.2">
+    <row r="119" spans="1:27" ht="19.149999999999999">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -17626,7 +17628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.2">
+    <row r="120" spans="1:27" ht="19.149999999999999">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -17688,7 +17690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.2">
+    <row r="121" spans="1:27" ht="19.149999999999999">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -17750,7 +17752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.2">
+    <row r="122" spans="1:27" ht="19.149999999999999">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -17812,7 +17814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.2">
+    <row r="123" spans="1:27" ht="19.149999999999999">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -17874,7 +17876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.2">
+    <row r="124" spans="1:27" ht="19.149999999999999">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -17936,7 +17938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.2">
+    <row r="125" spans="1:27" ht="19.149999999999999">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -17998,7 +18000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.2">
+    <row r="126" spans="1:27" ht="19.149999999999999">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -18060,7 +18062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.2">
+    <row r="127" spans="1:27" ht="19.149999999999999">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -18084,11 +18086,11 @@
       <c r="L127" s="29"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
-        <f t="shared" ref="N127" si="32">IF((J127-K127)&lt;0,0,(J127-K127))</f>
+        <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
         <v>0</v>
       </c>
       <c r="O127" s="5">
-        <f t="shared" ref="O127" si="33">IF((K127-J127)&lt;0,0,(K127-J127))</f>
+        <f t="shared" ref="O127" si="25">IF((K127-J127)&lt;0,0,(K127-J127))</f>
         <v>0</v>
       </c>
       <c r="P127" s="5"/>
@@ -18117,186 +18119,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -18316,8 +18138,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -18335,35 +18157,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:AB140"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" customWidth="1"/>
-    <col min="2" max="2" width="27.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" customWidth="1"/>
-    <col min="5" max="5" width="23.109375" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5546875" customWidth="1"/>
-    <col min="8" max="9" width="20.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="24.44140625" customWidth="1"/>
-    <col min="12" max="12" width="18.109375" customWidth="1"/>
-    <col min="13" max="15" width="20.88671875" customWidth="1"/>
-    <col min="16" max="16" width="21.5546875" customWidth="1"/>
-    <col min="17" max="17" width="29.109375" customWidth="1"/>
-    <col min="18" max="18" width="25.88671875" customWidth="1"/>
-    <col min="19" max="19" width="32.88671875" customWidth="1"/>
-    <col min="20" max="21" width="20.88671875" customWidth="1"/>
-    <col min="22" max="22" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="24.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" customWidth="1"/>
+    <col min="13" max="15" width="20.85546875" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" customWidth="1"/>
+    <col min="17" max="17" width="29.140625" customWidth="1"/>
+    <col min="18" max="18" width="25.85546875" customWidth="1"/>
+    <col min="19" max="19" width="32.85546875" customWidth="1"/>
+    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" customWidth="1"/>
     <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.33203125" customWidth="1"/>
-    <col min="25" max="25" width="20.88671875" customWidth="1"/>
-    <col min="26" max="26" width="14.88671875" customWidth="1"/>
-    <col min="27" max="27" width="15.109375" customWidth="1"/>
+    <col min="24" max="24" width="15.28515625" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.200000000000003" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
       <c r="D1" s="50" t="s">
         <v>34</v>
@@ -18481,7 +18303,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="38.4">
+    <row r="3" spans="1:27" ht="38.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -18520,11 +18342,11 @@
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
-        <f t="shared" ref="N3:N70" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
+        <f t="shared" ref="N3:N72" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
         <v>2872</v>
       </c>
       <c r="O3" s="5">
-        <f t="shared" ref="O3:O70" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
+        <f t="shared" ref="O3:O72" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
         <v>0</v>
       </c>
       <c r="P3" s="47">
@@ -18558,7 +18380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.2">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -18635,7 +18457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.2">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -18712,7 +18534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.2">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -18789,7 +18611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.2">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -18860,7 +18682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.2">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -18933,7 +18755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.2">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -19004,7 +18826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.2">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -19087,7 +18909,7 @@
       <c r="R11" s="49"/>
       <c r="S11" s="49"/>
     </row>
-    <row r="12" spans="1:27" ht="38.4">
+    <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -19164,7 +18986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.2">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -19241,7 +19063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.2">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -19316,7 +19138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.2">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -19387,7 +19209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.2">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -19464,7 +19286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.2">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -19535,7 +19357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.2">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -19606,7 +19428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.2">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -19689,7 +19511,7 @@
       <c r="R20" s="49"/>
       <c r="S20" s="49"/>
     </row>
-    <row r="21" spans="1:27" ht="38.4">
+    <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -19764,7 +19586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.2">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -19839,7 +19661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.2">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -19910,7 +19732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.2">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -19981,7 +19803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.2">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -20052,7 +19874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.2">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -20127,7 +19949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.2">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -20198,7 +20020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.2">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -20269,7 +20091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.2">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -20352,7 +20174,7 @@
       <c r="R30" s="49"/>
       <c r="S30" s="49"/>
     </row>
-    <row r="31" spans="1:27" ht="19.2">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -20423,7 +20245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.2">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -20494,7 +20316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.2">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -20565,7 +20387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.2">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -20636,7 +20458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="38.4">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -20707,7 +20529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.2">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -20778,7 +20600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.2">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -20849,7 +20671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.2">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -20920,7 +20742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.2">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -20991,7 +20813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.2">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -21062,7 +20884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.2">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -21145,7 +20967,7 @@
       <c r="R42" s="49"/>
       <c r="S42" s="49"/>
     </row>
-    <row r="43" spans="1:27" ht="19.2">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -21222,7 +21044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.2">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -21299,7 +21121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.2">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -21376,7 +21198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.2">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -21447,7 +21269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.4">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -21518,7 +21340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.2">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -21589,7 +21411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.2">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -21660,7 +21482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.2">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -21731,7 +21553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.2">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -21808,7 +21630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.2">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -21879,7 +21701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.2">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -21962,7 +21784,7 @@
       <c r="R54" s="49"/>
       <c r="S54" s="49"/>
     </row>
-    <row r="55" spans="1:27" ht="19.2">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -22051,7 +21873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.2">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -22146,7 +21968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.2">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -22241,7 +22063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.2">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -22324,7 +22146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="38.4">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -22407,7 +22229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.2">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -22490,7 +22312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.2">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -22573,7 +22395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.2">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -22650,7 +22472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.2">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -22721,7 +22543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.2">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -22804,7 +22626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.2">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -22893,7 +22715,7 @@
       <c r="R66" s="49"/>
       <c r="S66" s="49"/>
     </row>
-    <row r="67" spans="1:27" ht="19.2">
+    <row r="67" spans="1:27" ht="19.149999999999999">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -22962,7 +22784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.2">
+    <row r="68" spans="1:27" ht="19.149999999999999">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -23031,7 +22853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.2">
+    <row r="69" spans="1:27" ht="19.149999999999999">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -23100,7 +22922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.2">
+    <row r="70" spans="1:27" ht="19.149999999999999">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -23169,7 +22991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="38.4">
+    <row r="71" spans="1:27" ht="19.149999999999999">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -23238,7 +23060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.2">
+    <row r="72" spans="1:27" ht="19.149999999999999">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -23307,7 +23129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.2">
+    <row r="73" spans="1:27" ht="19.149999999999999">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -23376,7 +23198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.2">
+    <row r="74" spans="1:27" ht="19.149999999999999">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -23445,7 +23267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.2">
+    <row r="75" spans="1:27" ht="19.149999999999999">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -23514,7 +23336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.2">
+    <row r="76" spans="1:27" ht="19.149999999999999">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -23583,7 +23405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.2">
+    <row r="77" spans="1:27" ht="19.149999999999999">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -23658,7 +23480,7 @@
       <c r="R78" s="49"/>
       <c r="S78" s="49"/>
     </row>
-    <row r="79" spans="1:27" ht="19.2">
+    <row r="79" spans="1:27" ht="19.149999999999999">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -23689,11 +23511,11 @@
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
-        <f t="shared" ref="N79:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
+        <f t="shared" ref="N74:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
         <v>0</v>
       </c>
       <c r="O79" s="12">
-        <f t="shared" ref="O79:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
+        <f t="shared" ref="O74:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
         <v>0</v>
       </c>
       <c r="P79" s="47">
@@ -23727,7 +23549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.2">
+    <row r="80" spans="1:27" ht="19.149999999999999">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -23796,7 +23618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.2">
+    <row r="81" spans="1:27" ht="19.149999999999999">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -23865,7 +23687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.2">
+    <row r="82" spans="1:27" ht="19.149999999999999">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -23934,7 +23756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.2">
+    <row r="83" spans="1:27" ht="19.149999999999999">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -24003,7 +23825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.2">
+    <row r="84" spans="1:27" ht="19.149999999999999">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -24072,7 +23894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.2">
+    <row r="85" spans="1:27" ht="19.149999999999999">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -24141,7 +23963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.2">
+    <row r="86" spans="1:27" ht="19.149999999999999">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -24210,7 +24032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.2">
+    <row r="87" spans="1:27" ht="19.149999999999999">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -24279,7 +24101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.2">
+    <row r="88" spans="1:27" ht="19.149999999999999">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -24348,7 +24170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.2">
+    <row r="89" spans="1:27" ht="19.149999999999999">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -24423,7 +24245,7 @@
       <c r="R90" s="49"/>
       <c r="S90" s="49"/>
     </row>
-    <row r="91" spans="1:27" ht="19.2">
+    <row r="91" spans="1:27" ht="19.149999999999999">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -24492,7 +24314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.2">
+    <row r="92" spans="1:27" ht="19.149999999999999">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -24561,7 +24383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.2">
+    <row r="93" spans="1:27" ht="19.149999999999999">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -24630,7 +24452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.2">
+    <row r="94" spans="1:27" ht="19.149999999999999">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -24699,7 +24521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.2">
+    <row r="95" spans="1:27" ht="19.149999999999999">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -24768,7 +24590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.2">
+    <row r="96" spans="1:27" ht="19.149999999999999">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -24837,7 +24659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.2">
+    <row r="97" spans="1:27" ht="19.149999999999999">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -24906,7 +24728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.2">
+    <row r="98" spans="1:27" ht="19.149999999999999">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -24975,7 +24797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.2">
+    <row r="99" spans="1:27" ht="19.149999999999999">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -25044,7 +24866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.2">
+    <row r="100" spans="1:27" ht="19.149999999999999">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -25113,7 +24935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.2">
+    <row r="101" spans="1:27" ht="19.149999999999999">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -25188,7 +25010,7 @@
       <c r="R102" s="49"/>
       <c r="S102" s="49"/>
     </row>
-    <row r="103" spans="1:27" ht="19.2">
+    <row r="103" spans="1:27" ht="19.149999999999999">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -25257,7 +25079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.2">
+    <row r="104" spans="1:27" ht="19.149999999999999">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -25326,7 +25148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.2">
+    <row r="105" spans="1:27" ht="19.149999999999999">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -25395,7 +25217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.2">
+    <row r="106" spans="1:27" ht="19.149999999999999">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -25464,7 +25286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.2">
+    <row r="107" spans="1:27" ht="19.149999999999999">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -25533,7 +25355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.2">
+    <row r="108" spans="1:27" ht="19.149999999999999">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -25602,7 +25424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.2">
+    <row r="109" spans="1:27" ht="19.149999999999999">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -25671,7 +25493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.2">
+    <row r="110" spans="1:27" ht="19.149999999999999">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -25740,7 +25562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.2">
+    <row r="111" spans="1:27" ht="19.149999999999999">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -25809,7 +25631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.2">
+    <row r="112" spans="1:27" ht="19.149999999999999">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -25878,7 +25700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.2">
+    <row r="113" spans="1:28" ht="19.149999999999999">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -25953,7 +25775,7 @@
       <c r="R114" s="49"/>
       <c r="S114" s="49"/>
     </row>
-    <row r="115" spans="1:28" ht="38.4">
+    <row r="115" spans="1:28" ht="38.450000000000003">
       <c r="A115" s="1" t="s">
         <v>25</v>
       </c>
@@ -26022,7 +25844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.2">
+    <row r="116" spans="1:28" ht="19.149999999999999">
       <c r="A116" s="1" t="s">
         <v>25</v>
       </c>
@@ -26091,7 +25913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.2">
+    <row r="117" spans="1:28" ht="19.149999999999999">
       <c r="A117" s="1" t="s">
         <v>25</v>
       </c>
@@ -26160,7 +25982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.2">
+    <row r="118" spans="1:28" ht="19.149999999999999">
       <c r="A118" s="1" t="s">
         <v>25</v>
       </c>
@@ -26229,7 +26051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.4">
+    <row r="119" spans="1:28" ht="38.450000000000003">
       <c r="A119" s="1" t="s">
         <v>25</v>
       </c>
@@ -26298,7 +26120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="38.4">
+    <row r="120" spans="1:28" ht="19.149999999999999">
       <c r="A120" s="1" t="s">
         <v>25</v>
       </c>
@@ -26367,7 +26189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="57.6">
+    <row r="121" spans="1:28" ht="38.450000000000003">
       <c r="A121" s="1" t="s">
         <v>25</v>
       </c>
@@ -26436,7 +26258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.4">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>25</v>
       </c>
@@ -27016,186 +26838,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C67:C77 C79:C89 C115:C122 C103:C113 C91:C101 C2:C10 C12:C19 C21:C29" name="Textbooks"/>
@@ -27218,8 +26860,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
